--- a/excel-files/MANDALUYONG/PLEASANT HILLS ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/MANDALUYONG/PLEASANT HILLS ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64DE7D50-7E3F-4AF1-9E07-79516535A9A9}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{382869F5-732D-4FC3-8C64-7322E8D6F0B0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -320,7 +320,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,6 +423,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
@@ -631,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -747,6 +753,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3470,6 +3485,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H98"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
@@ -5344,14 +5362,15 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="6" fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -5360,68 +5379,59 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AA157"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="6" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="21.28515625" customWidth="1"/>
     <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="13" max="16" width="10.28515625" customWidth="1"/>
+    <col min="17" max="17" width="21" customWidth="1"/>
+    <col min="18" max="22" width="10.5703125" customWidth="1"/>
+    <col min="23" max="23" width="21.28515625" customWidth="1"/>
+    <col min="24" max="27" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5585,11 +5595,11 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="36.75">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="1"/>
@@ -6150,11 +6160,11 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="36.75">
       <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="1"/>
@@ -6716,11 +6726,11 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="36.75">
       <c r="A23" s="1">
         <v>3</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="1"/>
@@ -7627,11 +7637,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="36.75">
       <c r="A37" s="1">
         <v>4</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="43" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="1"/>
@@ -8262,11 +8272,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="36.75">
       <c r="A47" s="1">
         <v>5</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="43" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="1"/>
@@ -8897,11 +8907,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="36.75">
       <c r="A57" s="1">
         <v>6</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="43" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="1"/>
@@ -9532,11 +9542,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="36.75">
       <c r="A67" s="10">
         <v>7</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="44" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="10"/>
@@ -13545,14 +13555,15 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="6" fitToHeight="0" orientation="landscape"/>
   <ignoredErrors>
     <ignoredError sqref="J5 P5:P6 V5" calculatedColumn="1"/>
   </ignoredErrors>
@@ -13564,70 +13575,64 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" customWidth="1"/>
+    <col min="6" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" customWidth="1"/>
+    <col min="12" max="13" width="11.5703125" customWidth="1"/>
+    <col min="14" max="16" width="14.7109375" customWidth="1"/>
+    <col min="17" max="17" width="23.7109375" customWidth="1"/>
+    <col min="18" max="19" width="12.140625" customWidth="1"/>
+    <col min="20" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="22.7109375" customWidth="1"/>
+    <col min="24" max="25" width="11.28515625" customWidth="1"/>
+    <col min="26" max="27" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -14266,11 +14271,11 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="25.5" customHeight="1">
+    <row r="12" spans="1:27" ht="32.25" customHeight="1">
       <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1"/>
@@ -14818,11 +14823,11 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="36.75">
       <c r="A21" s="1">
         <v>3</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="1"/>
@@ -15716,11 +15721,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="36.75">
       <c r="A35" s="1">
         <v>4</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="43" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="1"/>
@@ -16476,7 +16481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -21227,7 +21232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21807,186 +21812,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22000,16 +21825,19 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R91 L91 X91 F91" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F92:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L92:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R92:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X92:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{9F597708-9F99-4CC7-AD50-694240470AB5}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="6" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
